--- a/Financial Analysis/GME.xlsx
+++ b/Financial Analysis/GME.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107561BB-D8E2-49F6-BEF1-9C34DCC17173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF7C30C-B1AB-4ECA-920E-128FADDB57D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{B9889FC1-6C81-4A49-B2B3-546123B256CC}"/>
   </bookViews>
@@ -1010,14 +1010,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>23.93</v>
+        <v>22.03</v>
       </c>
       <c r="E3" s="4">
-        <v>45909</v>
+        <v>45964</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45964</v>
       </c>
       <c r="G3" s="4">
         <v>46000</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>10706.281999999999</v>
+        <v>9856.2219999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>6172.7819999999992</v>
+        <v>5322.7219999999998</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -1715,7 +1715,7 @@
         <v>2000.8664841599998</v>
       </c>
       <c r="BT3" s="5">
-        <f t="shared" ref="BR3:BZ4" si="0">BS3*1.01</f>
+        <f t="shared" ref="BT3:BZ4" si="0">BS3*1.01</f>
         <v>2020.8751490015998</v>
       </c>
       <c r="BU3" s="5">
@@ -1877,7 +1877,7 @@
         <v>804.58620000000008</v>
       </c>
       <c r="BR4" s="5">
-        <f t="shared" ref="BR4:BZ5" si="1">BQ4*1.02</f>
+        <f t="shared" ref="BR4:BU4" si="1">BQ4*1.02</f>
         <v>820.67792400000008</v>
       </c>
       <c r="BS4" s="5">
@@ -2502,7 +2502,7 @@
         <v>689.1</v>
       </c>
       <c r="BA7" s="13">
-        <f t="shared" ref="AZ7:BB7" si="6">BA6-BA8</f>
+        <f t="shared" ref="BA7:BB7" si="6">BA6-BA8</f>
         <v>634.59640000000002</v>
       </c>
       <c r="BB7" s="13">
@@ -4549,7 +4549,7 @@
         <v>6</v>
       </c>
       <c r="BA15" s="13">
-        <f t="shared" ref="AZ15:BB15" si="30">BA14*0.16</f>
+        <f t="shared" ref="BA15:BB15" si="30">BA14*0.16</f>
         <v>22.302976000000005</v>
       </c>
       <c r="BB15" s="13">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="CC36" s="6">
         <f>Main!D3</f>
-        <v>23.93</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="37" spans="2:81" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="CC37" s="12">
         <f>CC35/CC36-1</f>
-        <v>9.7529152629199478E-2</v>
+        <v>0.19218668281510398</v>
       </c>
     </row>
     <row r="38" spans="2:81" x14ac:dyDescent="0.3">
@@ -12271,13 +12271,13 @@
       </c>
       <c r="CC82">
         <f>Main!D3</f>
-        <v>23.93</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="83" spans="80:81" x14ac:dyDescent="0.3">
       <c r="CC83" s="12">
         <f>CC81/CC82-1</f>
-        <v>0.12464003865324158</v>
+        <v>0.22163577507816923</v>
       </c>
     </row>
   </sheetData>
